--- a/LIPIDOMICS_Calculation/LipidMapsInvData.xlsx
+++ b/LIPIDOMICS_Calculation/LipidMapsInvData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niethamp\Box\Yanan Ma (Collaborate)\5-HEDH paper\second version\Figures_20250105_PN_YNM\Figure_Reordering 250110\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Redox-DHRS7_subcellular\LIPIDOMICS_Calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3F08B2-2391-42D7-B770-CDF0FF080130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B372B-A5FA-4841-ADE7-11C5B44E4AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3450" windowWidth="29040" windowHeight="15840" xr2:uid="{E5471A1B-BC7E-4CB8-BAD3-9E5C4A6BAB04}"/>
+    <workbookView xWindow="12105" yWindow="2220" windowWidth="38700" windowHeight="15345" xr2:uid="{E5471A1B-BC7E-4CB8-BAD3-9E5C4A6BAB04}"/>
   </bookViews>
   <sheets>
     <sheet name="LipidMapsSD data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sample_Metadata" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="133">
   <si>
     <t>bicyclo PGE2</t>
   </si>
@@ -296,37 +297,142 @@
     <t>Ttest</t>
   </si>
   <si>
+    <t>Lipid</t>
+  </si>
+  <si>
+    <t>WT_F1</t>
+  </si>
+  <si>
+    <t>WT_F2</t>
+  </si>
+  <si>
+    <t>WT_F3</t>
+  </si>
+  <si>
+    <t>WT_M1</t>
+  </si>
+  <si>
+    <t>WT_M2</t>
+  </si>
+  <si>
+    <t>WT_M3</t>
+  </si>
+  <si>
+    <t>KO_F1</t>
+  </si>
+  <si>
+    <t>KO_F2</t>
+  </si>
+  <si>
+    <t>KO_F3</t>
+  </si>
+  <si>
+    <t>KO_M1</t>
+  </si>
+  <si>
+    <t>KO_M2</t>
+  </si>
+  <si>
+    <t>KO_M3</t>
+  </si>
+  <si>
+    <t>DataColumn</t>
+  </si>
+  <si>
+    <t>OriginalHeader</t>
+  </si>
+  <si>
+    <t>SampleID</t>
+  </si>
+  <si>
+    <t>Genotype</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Replicate</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Wt_1</t>
   </si>
   <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Wt_2</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>Wt_3</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>Wt_4</t>
   </si>
   <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Wt_5</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>Wt_6</t>
   </si>
   <si>
+    <t>H</t>
+  </si>
+  <si>
     <t>KO_1</t>
   </si>
   <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
     <t>KO_2</t>
   </si>
   <si>
+    <t>J</t>
+  </si>
+  <si>
     <t>KO_3</t>
   </si>
   <si>
+    <t>K</t>
+  </si>
+  <si>
     <t>KO_4</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>KO_5</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>KO_6</t>
@@ -336,7 +442,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,16 +464,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -375,13 +506,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E78"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1F4E78"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,9 +610,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -440,7 +650,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -546,7 +756,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -688,7 +898,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -697,47 +907,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0088FDE-0323-4021-94E0-248ED5B47E2F}">
   <dimension ref="A1:P85"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>86</v>
+      </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N1" t="s">
         <v>84</v>
@@ -746,7 +959,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,19 +1000,19 @@
         <v>3.372923616491609E-3</v>
       </c>
       <c r="N2" s="1">
-        <f>AVERAGE(H2:M2)/AVERAGE(B2:G2)</f>
+        <f t="shared" ref="N2:N33" si="0">AVERAGE(H2:M2)/AVERAGE(B2:G2)</f>
         <v>0.44233189558017522</v>
       </c>
       <c r="O2" s="1">
-        <f>TTEST(H2:M2,B2:G2,2,3)</f>
+        <f t="shared" ref="O2:O33" si="1">TTEST(H2:M2,B2:G2,2,3)</f>
         <v>4.5738631145687087E-3</v>
       </c>
       <c r="P2" s="1">
-        <f>(N2-1)*100</f>
+        <f t="shared" ref="P2:P33" si="2">(N2-1)*100</f>
         <v>-55.766810441982486</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -840,19 +1053,19 @@
         <v>1.2500187848899051E-2</v>
       </c>
       <c r="N3" s="1">
-        <f>AVERAGE(H3:M3)/AVERAGE(B3:G3)</f>
+        <f t="shared" si="0"/>
         <v>0.73521596823622748</v>
       </c>
       <c r="O3" s="1">
-        <f>TTEST(H3:M3,B3:G3,2,3)</f>
+        <f t="shared" si="1"/>
         <v>6.0368674505838493E-3</v>
       </c>
       <c r="P3" s="1">
-        <f>(N3-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-26.478403176377252</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -893,19 +1106,19 @@
         <v>3.0494366730685899E-2</v>
       </c>
       <c r="N4" s="1">
-        <f>AVERAGE(H4:M4)/AVERAGE(B4:G4)</f>
+        <f t="shared" si="0"/>
         <v>0.64804221701170994</v>
       </c>
       <c r="O4" s="1">
-        <f>TTEST(H4:M4,B4:G4,2,3)</f>
+        <f t="shared" si="1"/>
         <v>7.6022821411070671E-3</v>
       </c>
       <c r="P4" s="1">
-        <f>(N4-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-35.195778298829005</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -946,19 +1159,19 @@
         <v>1.7926669503796022E-2</v>
       </c>
       <c r="N5" s="1">
-        <f>AVERAGE(H5:M5)/AVERAGE(B5:G5)</f>
+        <f t="shared" si="0"/>
         <v>0.66307781946724109</v>
       </c>
       <c r="O5" s="1">
-        <f>TTEST(H5:M5,B5:G5,2,3)</f>
+        <f t="shared" si="1"/>
         <v>1.6433145743730407E-2</v>
       </c>
       <c r="P5" s="1">
-        <f>(N5-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-33.692218053275894</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -999,19 +1212,19 @@
         <v>0.42612166749074021</v>
       </c>
       <c r="N6" s="1">
-        <f>AVERAGE(H6:M6)/AVERAGE(B6:G6)</f>
+        <f t="shared" si="0"/>
         <v>0.61046894483144343</v>
       </c>
       <c r="O6" s="1">
-        <f>TTEST(H6:M6,B6:G6,2,3)</f>
+        <f t="shared" si="1"/>
         <v>1.7973681443416732E-2</v>
       </c>
       <c r="P6" s="1">
-        <f>(N6-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-38.953105516855658</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1052,19 +1265,19 @@
         <v>4.3772896449833183E-2</v>
       </c>
       <c r="N7" s="1">
-        <f>AVERAGE(H7:M7)/AVERAGE(B7:G7)</f>
+        <f t="shared" si="0"/>
         <v>0.69434488858603016</v>
       </c>
       <c r="O7" s="1">
-        <f>TTEST(H7:M7,B7:G7,2,3)</f>
+        <f t="shared" si="1"/>
         <v>2.1604643506710413E-2</v>
       </c>
       <c r="P7" s="1">
-        <f>(N7-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-30.565511141396982</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1105,19 +1318,19 @@
         <v>8.1565129462496779E-4</v>
       </c>
       <c r="N8" s="1">
-        <f>AVERAGE(H8:M8)/AVERAGE(B8:G8)</f>
+        <f t="shared" si="0"/>
         <v>0.51975951294461253</v>
       </c>
       <c r="O8" s="1">
-        <f>TTEST(H8:M8,B8:G8,2,3)</f>
+        <f t="shared" si="1"/>
         <v>2.7059917810220387E-2</v>
       </c>
       <c r="P8" s="1">
-        <f>(N8-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-48.024048705538746</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1158,19 +1371,19 @@
         <v>5.2065144211760773E-4</v>
       </c>
       <c r="N9" s="1">
-        <f>AVERAGE(H9:M9)/AVERAGE(B9:G9)</f>
+        <f t="shared" si="0"/>
         <v>0.56978369109546123</v>
       </c>
       <c r="O9" s="1">
-        <f>TTEST(H9:M9,B9:G9,2,3)</f>
+        <f t="shared" si="1"/>
         <v>2.9229627635611859E-2</v>
       </c>
       <c r="P9" s="1">
-        <f>(N9-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-43.021630890453878</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1211,19 +1424,19 @@
         <v>4.7096457254366869E-2</v>
       </c>
       <c r="N10" s="1">
-        <f>AVERAGE(H10:M10)/AVERAGE(B10:G10)</f>
+        <f t="shared" si="0"/>
         <v>1.9538210847152959</v>
       </c>
       <c r="O10" s="1">
-        <f>TTEST(H10:M10,B10:G10,2,3)</f>
+        <f t="shared" si="1"/>
         <v>3.3959064508322798E-2</v>
       </c>
       <c r="P10" s="1">
-        <f>(N10-1)*100</f>
+        <f t="shared" si="2"/>
         <v>95.382108471529591</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1264,19 +1477,19 @@
         <v>8.4465060605720659E-3</v>
       </c>
       <c r="N11">
-        <f>AVERAGE(H11:M11)/AVERAGE(B11:G11)</f>
+        <f t="shared" si="0"/>
         <v>0.38348186319085464</v>
       </c>
       <c r="O11">
-        <f>TTEST(H11:M11,B11:G11,2,3)</f>
+        <f t="shared" si="1"/>
         <v>5.4177091851804374E-2</v>
       </c>
       <c r="P11" s="1">
-        <f>(N11-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-61.651813680914536</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1317,19 +1530,19 @@
         <v>0.62904851358702973</v>
       </c>
       <c r="N12">
-        <f>AVERAGE(H12:M12)/AVERAGE(B12:G12)</f>
+        <f t="shared" si="0"/>
         <v>0.65393154940599685</v>
       </c>
       <c r="O12">
-        <f>TTEST(H12:M12,B12:G12,2,3)</f>
+        <f t="shared" si="1"/>
         <v>6.5023880998148834E-2</v>
       </c>
       <c r="P12" s="1">
-        <f>(N12-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-34.606845059400314</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1370,19 +1583,19 @@
         <v>4.1566519684947852E-3</v>
       </c>
       <c r="N13">
-        <f>AVERAGE(H13:M13)/AVERAGE(B13:G13)</f>
+        <f t="shared" si="0"/>
         <v>0.71984070352474883</v>
       </c>
       <c r="O13">
-        <f>TTEST(H13:M13,B13:G13,2,3)</f>
+        <f t="shared" si="1"/>
         <v>7.2582206757422843E-2</v>
       </c>
       <c r="P13" s="1">
-        <f>(N13-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-28.015929647525116</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1423,19 +1636,19 @@
         <v>3.1453569526902314E-2</v>
       </c>
       <c r="N14">
-        <f>AVERAGE(H14:M14)/AVERAGE(B14:G14)</f>
+        <f t="shared" si="0"/>
         <v>0.77036121772575472</v>
       </c>
       <c r="O14">
-        <f>TTEST(H14:M14,B14:G14,2,3)</f>
+        <f t="shared" si="1"/>
         <v>7.6896247891765385E-2</v>
       </c>
       <c r="P14" s="1">
-        <f>(N14-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-22.963878227424527</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1476,19 +1689,19 @@
         <v>5.7063666606141698E-2</v>
       </c>
       <c r="N15">
-        <f>AVERAGE(H15:M15)/AVERAGE(B15:G15)</f>
+        <f t="shared" si="0"/>
         <v>0.75710017470510693</v>
       </c>
       <c r="O15">
-        <f>TTEST(H15:M15,B15:G15,2,3)</f>
+        <f t="shared" si="1"/>
         <v>8.2754436323635022E-2</v>
       </c>
       <c r="P15" s="1">
-        <f>(N15-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-24.289982529489308</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1529,19 +1742,19 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f>AVERAGE(H16:M16)/AVERAGE(B16:G16)</f>
+        <f t="shared" si="0"/>
         <v>0.21821268592092441</v>
       </c>
       <c r="O16">
-        <f>TTEST(H16:M16,B16:G16,2,3)</f>
+        <f t="shared" si="1"/>
         <v>8.9423811418932422E-2</v>
       </c>
       <c r="P16" s="1">
-        <f>(N16-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-78.178731407907563</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1582,19 +1795,19 @@
         <v>5.3248387982554143E-2</v>
       </c>
       <c r="N17">
-        <f>AVERAGE(H17:M17)/AVERAGE(B17:G17)</f>
+        <f t="shared" si="0"/>
         <v>0.82139287140981321</v>
       </c>
       <c r="O17">
-        <f>TTEST(H17:M17,B17:G17,2,3)</f>
+        <f t="shared" si="1"/>
         <v>9.2653956142413008E-2</v>
       </c>
       <c r="P17" s="1">
-        <f>(N17-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-17.86071285901868</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1635,19 +1848,19 @@
         <v>1.0788562599123354E-3</v>
       </c>
       <c r="N18">
-        <f>AVERAGE(H18:M18)/AVERAGE(B18:G18)</f>
+        <f t="shared" si="0"/>
         <v>0.72613948227448299</v>
       </c>
       <c r="O18">
-        <f>TTEST(H18:M18,B18:G18,2,3)</f>
+        <f t="shared" si="1"/>
         <v>9.5497547511594075E-2</v>
       </c>
       <c r="P18" s="1">
-        <f>(N18-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-27.386051772551699</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1688,19 +1901,19 @@
         <v>83.102670217743025</v>
       </c>
       <c r="N19">
-        <f>AVERAGE(H19:M19)/AVERAGE(B19:G19)</f>
+        <f t="shared" si="0"/>
         <v>0.86315056277390489</v>
       </c>
       <c r="O19">
-        <f>TTEST(H19:M19,B19:G19,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.11129553649030294</v>
       </c>
       <c r="P19" s="1">
-        <f>(N19-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-13.684943722609511</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1741,19 +1954,19 @@
         <v>1.4978948828220007E-2</v>
       </c>
       <c r="N20">
-        <f>AVERAGE(H20:M20)/AVERAGE(B20:G20)</f>
+        <f t="shared" si="0"/>
         <v>0.79197196671231762</v>
       </c>
       <c r="O20">
-        <f>TTEST(H20:M20,B20:G20,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.11544743900550038</v>
       </c>
       <c r="P20" s="1">
-        <f>(N20-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-20.802803328768238</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1794,19 +2007,19 @@
         <v>0.44594242842905668</v>
       </c>
       <c r="N21">
-        <f>AVERAGE(H21:M21)/AVERAGE(B21:G21)</f>
+        <f t="shared" si="0"/>
         <v>1.2861042561475189</v>
       </c>
       <c r="O21">
-        <f>TTEST(H21:M21,B21:G21,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.12045487038439209</v>
       </c>
       <c r="P21" s="1">
-        <f>(N21-1)*100</f>
+        <f t="shared" si="2"/>
         <v>28.61042561475189</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -1847,19 +2060,19 @@
         <v>5.2492688727206502</v>
       </c>
       <c r="N22">
-        <f>AVERAGE(H22:M22)/AVERAGE(B22:G22)</f>
+        <f t="shared" si="0"/>
         <v>0.70631024883473226</v>
       </c>
       <c r="O22">
-        <f>TTEST(H22:M22,B22:G22,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.12050388049550413</v>
       </c>
       <c r="P22" s="1">
-        <f>(N22-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-29.368975116526773</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1900,19 +2113,19 @@
         <v>1.6295607929845877</v>
       </c>
       <c r="N23">
-        <f>AVERAGE(H23:M23)/AVERAGE(B23:G23)</f>
+        <f t="shared" si="0"/>
         <v>1.4406336004600722</v>
       </c>
       <c r="O23">
-        <f>TTEST(H23:M23,B23:G23,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.12334755350461878</v>
       </c>
       <c r="P23" s="1">
-        <f>(N23-1)*100</f>
+        <f t="shared" si="2"/>
         <v>44.063360046007219</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1953,19 +2166,19 @@
         <v>0.2573408969624566</v>
       </c>
       <c r="N24">
-        <f>AVERAGE(H24:M24)/AVERAGE(B24:G24)</f>
+        <f t="shared" si="0"/>
         <v>0.77759752215966405</v>
       </c>
       <c r="O24">
-        <f>TTEST(H24:M24,B24:G24,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.13670043927591025</v>
       </c>
       <c r="P24" s="1">
-        <f>(N24-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-22.240247784033595</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2006,19 +2219,19 @@
         <v>8.0492766857731424E-3</v>
       </c>
       <c r="N25">
-        <f>AVERAGE(H25:M25)/AVERAGE(B25:G25)</f>
+        <f t="shared" si="0"/>
         <v>0.79716899322693202</v>
       </c>
       <c r="O25">
-        <f>TTEST(H25:M25,B25:G25,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.13894817123313744</v>
       </c>
       <c r="P25" s="1">
-        <f>(N25-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-20.283100677306798</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2059,19 +2272,19 @@
         <v>1.734089730840635E-2</v>
       </c>
       <c r="N26">
-        <f>AVERAGE(H26:M26)/AVERAGE(B26:G26)</f>
+        <f t="shared" si="0"/>
         <v>0.80782500755986364</v>
       </c>
       <c r="O26">
-        <f>TTEST(H26:M26,B26:G26,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.14459986011572515</v>
       </c>
       <c r="P26" s="1">
-        <f>(N26-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-19.217499244013638</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2112,19 +2325,19 @@
         <v>5.2903457725687907E-2</v>
       </c>
       <c r="N27">
-        <f>AVERAGE(H27:M27)/AVERAGE(B27:G27)</f>
+        <f t="shared" si="0"/>
         <v>0.75245896689184932</v>
       </c>
       <c r="O27">
-        <f>TTEST(H27:M27,B27:G27,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.1535079539653296</v>
       </c>
       <c r="P27" s="1">
-        <f>(N27-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-24.754103310815069</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -2165,19 +2378,19 @@
         <v>66.870675002598944</v>
       </c>
       <c r="N28">
-        <f>AVERAGE(H28:M28)/AVERAGE(B28:G28)</f>
+        <f t="shared" si="0"/>
         <v>0.88269096725165241</v>
       </c>
       <c r="O28">
-        <f>TTEST(H28:M28,B28:G28,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.16034467210033398</v>
       </c>
       <c r="P28" s="1">
-        <f>(N28-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-11.730903274834759</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2218,19 +2431,19 @@
         <v>7.1713468194793503E-2</v>
       </c>
       <c r="N29">
-        <f>AVERAGE(H29:M29)/AVERAGE(B29:G29)</f>
+        <f t="shared" si="0"/>
         <v>1.1972137006002292</v>
       </c>
       <c r="O29">
-        <f>TTEST(H29:M29,B29:G29,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.17940837864294351</v>
       </c>
       <c r="P29" s="1">
-        <f>(N29-1)*100</f>
+        <f t="shared" si="2"/>
         <v>19.721370060022924</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2271,19 +2484,19 @@
         <v>1.8448376422660429E-3</v>
       </c>
       <c r="N30">
-        <f>AVERAGE(H30:M30)/AVERAGE(B30:G30)</f>
+        <f t="shared" si="0"/>
         <v>0.83914738397598276</v>
       </c>
       <c r="O30">
-        <f>TTEST(H30:M30,B30:G30,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.19331461204227873</v>
       </c>
       <c r="P30" s="1">
-        <f>(N30-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-16.085261602401722</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2324,19 +2537,19 @@
         <v>0.41541042439706583</v>
       </c>
       <c r="N31">
-        <f>AVERAGE(H31:M31)/AVERAGE(B31:G31)</f>
+        <f t="shared" si="0"/>
         <v>1.4635166269779061</v>
       </c>
       <c r="O31">
-        <f>TTEST(H31:M31,B31:G31,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.20095150431506839</v>
       </c>
       <c r="P31" s="1">
-        <f>(N31-1)*100</f>
+        <f t="shared" si="2"/>
         <v>46.351662697790609</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2377,19 +2590,19 @@
         <v>1.5996897488306668E-3</v>
       </c>
       <c r="N32">
-        <f>AVERAGE(H32:M32)/AVERAGE(B32:G32)</f>
+        <f t="shared" si="0"/>
         <v>0.73426914505016561</v>
       </c>
       <c r="O32">
-        <f>TTEST(H32:M32,B32:G32,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.22169064157072407</v>
       </c>
       <c r="P32" s="1">
-        <f>(N32-1)*100</f>
+        <f t="shared" si="2"/>
         <v>-26.573085494983438</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2430,19 +2643,19 @@
         <v>0.45636181759482269</v>
       </c>
       <c r="N33">
-        <f>AVERAGE(H33:M33)/AVERAGE(B33:G33)</f>
+        <f t="shared" si="0"/>
         <v>1.2754084314986527</v>
       </c>
       <c r="O33">
-        <f>TTEST(H33:M33,B33:G33,2,3)</f>
+        <f t="shared" si="1"/>
         <v>0.22469330049077774</v>
       </c>
       <c r="P33" s="1">
-        <f>(N33-1)*100</f>
+        <f t="shared" si="2"/>
         <v>27.540843149865267</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2483,19 +2696,19 @@
         <v>6.7608008660870161E-2</v>
       </c>
       <c r="N34">
-        <f>AVERAGE(H34:M34)/AVERAGE(B34:G34)</f>
+        <f t="shared" ref="N34:N65" si="3">AVERAGE(H34:M34)/AVERAGE(B34:G34)</f>
         <v>1.1896102561203989</v>
       </c>
       <c r="O34">
-        <f>TTEST(H34:M34,B34:G34,2,3)</f>
+        <f t="shared" ref="O34:O65" si="4">TTEST(H34:M34,B34:G34,2,3)</f>
         <v>0.23415125629723466</v>
       </c>
       <c r="P34" s="1">
-        <f>(N34-1)*100</f>
+        <f t="shared" ref="P34:P65" si="5">(N34-1)*100</f>
         <v>18.961025612039894</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2536,19 +2749,19 @@
         <v>1.2740880975004038E-3</v>
       </c>
       <c r="N35">
-        <f>AVERAGE(H35:M35)/AVERAGE(B35:G35)</f>
+        <f t="shared" si="3"/>
         <v>0.79808887597103373</v>
       </c>
       <c r="O35">
-        <f>TTEST(H35:M35,B35:G35,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.24464004989464783</v>
       </c>
       <c r="P35" s="1">
-        <f>(N35-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-20.191112402896628</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -2589,19 +2802,19 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <f>AVERAGE(H36:M36)/AVERAGE(B36:G36)</f>
+        <f t="shared" si="3"/>
         <v>0.4830514608818009</v>
       </c>
       <c r="O36">
-        <f>TTEST(H36:M36,B36:G36,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.25820126183811559</v>
       </c>
       <c r="P36" s="1">
-        <f>(N36-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-51.694853911819919</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2642,19 +2855,19 @@
         <v>3.9671960866910085E-2</v>
       </c>
       <c r="N37">
-        <f>AVERAGE(H37:M37)/AVERAGE(B37:G37)</f>
+        <f t="shared" si="3"/>
         <v>0.73813019416288039</v>
       </c>
       <c r="O37">
-        <f>TTEST(H37:M37,B37:G37,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.25920323007335599</v>
       </c>
       <c r="P37" s="1">
-        <f>(N37-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-26.186980583711961</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2695,19 +2908,19 @@
         <v>1.0815112922914316E-3</v>
       </c>
       <c r="N38">
-        <f>AVERAGE(H38:M38)/AVERAGE(B38:G38)</f>
+        <f t="shared" si="3"/>
         <v>0.82703210416626005</v>
       </c>
       <c r="O38">
-        <f>TTEST(H38:M38,B38:G38,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.28645233704116674</v>
       </c>
       <c r="P38" s="1">
-        <f>(N38-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-17.296789583373993</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2748,19 +2961,19 @@
         <v>0.15853270829140131</v>
       </c>
       <c r="N39">
-        <f>AVERAGE(H39:M39)/AVERAGE(B39:G39)</f>
+        <f t="shared" si="3"/>
         <v>1.38881183851815</v>
       </c>
       <c r="O39">
-        <f>TTEST(H39:M39,B39:G39,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.30110615493946774</v>
       </c>
       <c r="P39" s="1">
-        <f>(N39-1)*100</f>
+        <f t="shared" si="5"/>
         <v>38.881183851815003</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2801,19 +3014,19 @@
         <v>1.3378991125003074E-2</v>
       </c>
       <c r="N40">
-        <f>AVERAGE(H40:M40)/AVERAGE(B40:G40)</f>
+        <f t="shared" si="3"/>
         <v>1.3005174396605479</v>
       </c>
       <c r="O40">
-        <f>TTEST(H40:M40,B40:G40,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.30263590410977792</v>
       </c>
       <c r="P40" s="1">
-        <f>(N40-1)*100</f>
+        <f t="shared" si="5"/>
         <v>30.05174396605479</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -2854,19 +3067,19 @@
         <v>6.1182545992190328E-2</v>
       </c>
       <c r="N41">
-        <f>AVERAGE(H41:M41)/AVERAGE(B41:G41)</f>
+        <f t="shared" si="3"/>
         <v>1.1801800638420201</v>
       </c>
       <c r="O41">
-        <f>TTEST(H41:M41,B41:G41,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.30548498128986634</v>
       </c>
       <c r="P41" s="1">
-        <f>(N41-1)*100</f>
+        <f t="shared" si="5"/>
         <v>18.01800638420201</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2907,19 +3120,19 @@
         <v>1.7143274743704553E-2</v>
       </c>
       <c r="N42">
-        <f>AVERAGE(H42:M42)/AVERAGE(B42:G42)</f>
+        <f t="shared" si="3"/>
         <v>0.7543423961370237</v>
       </c>
       <c r="O42">
-        <f>TTEST(H42:M42,B42:G42,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.31071875749753236</v>
       </c>
       <c r="P42" s="1">
-        <f>(N42-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-24.565760386297629</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -2960,19 +3173,19 @@
         <v>2.0028345922990982E-2</v>
       </c>
       <c r="N43">
-        <f>AVERAGE(H43:M43)/AVERAGE(B43:G43)</f>
+        <f t="shared" si="3"/>
         <v>0.83306938316010337</v>
       </c>
       <c r="O43">
-        <f>TTEST(H43:M43,B43:G43,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.33220181575822993</v>
       </c>
       <c r="P43" s="1">
-        <f>(N43-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-16.693061683989662</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3013,19 +3226,19 @@
         <v>3.0865864104420988E-3</v>
       </c>
       <c r="N44">
-        <f>AVERAGE(H44:M44)/AVERAGE(B44:G44)</f>
+        <f t="shared" si="3"/>
         <v>1.1529578982189461</v>
       </c>
       <c r="O44">
-        <f>TTEST(H44:M44,B44:G44,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.33252579841668062</v>
       </c>
       <c r="P44" s="1">
-        <f>(N44-1)*100</f>
+        <f t="shared" si="5"/>
         <v>15.295789821894612</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3066,19 +3279,19 @@
         <v>1.3748760573982931E-2</v>
       </c>
       <c r="N45">
-        <f>AVERAGE(H45:M45)/AVERAGE(B45:G45)</f>
+        <f t="shared" si="3"/>
         <v>1.2725967624452086</v>
       </c>
       <c r="O45">
-        <f>TTEST(H45:M45,B45:G45,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.34475367454258221</v>
       </c>
       <c r="P45" s="1">
-        <f>(N45-1)*100</f>
+        <f t="shared" si="5"/>
         <v>27.259676244520858</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3119,19 +3332,19 @@
         <v>0.17323992599500773</v>
       </c>
       <c r="N46">
-        <f>AVERAGE(H46:M46)/AVERAGE(B46:G46)</f>
+        <f t="shared" si="3"/>
         <v>1.2844021237393239</v>
       </c>
       <c r="O46">
-        <f>TTEST(H46:M46,B46:G46,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.34627416629556179</v>
       </c>
       <c r="P46" s="1">
-        <f>(N46-1)*100</f>
+        <f t="shared" si="5"/>
         <v>28.440212373932393</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3172,19 +3385,19 @@
         <v>5.2506234828973875E-2</v>
       </c>
       <c r="N47">
-        <f>AVERAGE(H47:M47)/AVERAGE(B47:G47)</f>
+        <f t="shared" si="3"/>
         <v>0.85872266920842011</v>
       </c>
       <c r="O47">
-        <f>TTEST(H47:M47,B47:G47,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.34725345792439771</v>
       </c>
       <c r="P47" s="1">
-        <f>(N47-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-14.12773307915799</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3225,19 +3438,19 @@
         <v>3.6534042659590541E-3</v>
       </c>
       <c r="N48">
-        <f>AVERAGE(H48:M48)/AVERAGE(B48:G48)</f>
+        <f t="shared" si="3"/>
         <v>0.82394589549318276</v>
       </c>
       <c r="O48">
-        <f>TTEST(H48:M48,B48:G48,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.35175040607560426</v>
       </c>
       <c r="P48" s="1">
-        <f>(N48-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-17.605410450681724</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3278,19 +3491,19 @@
         <v>6.1124679174799711E-2</v>
       </c>
       <c r="N49">
-        <f>AVERAGE(H49:M49)/AVERAGE(B49:G49)</f>
+        <f t="shared" si="3"/>
         <v>0.88233362708430629</v>
       </c>
       <c r="O49">
-        <f>TTEST(H49:M49,B49:G49,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.36093824824671528</v>
       </c>
       <c r="P49" s="1">
-        <f>(N49-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-11.766637291569371</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3331,19 +3544,19 @@
         <v>0.10148841632626369</v>
       </c>
       <c r="N50">
-        <f>AVERAGE(H50:M50)/AVERAGE(B50:G50)</f>
+        <f t="shared" si="3"/>
         <v>0.85406588184267762</v>
       </c>
       <c r="O50">
-        <f>TTEST(H50:M50,B50:G50,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.37662571532797473</v>
       </c>
       <c r="P50" s="1">
-        <f>(N50-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-14.593411815732239</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3384,19 +3597,19 @@
         <v>5.3717687703122E-4</v>
       </c>
       <c r="N51">
-        <f>AVERAGE(H51:M51)/AVERAGE(B51:G51)</f>
+        <f t="shared" si="3"/>
         <v>0.63543870598974328</v>
       </c>
       <c r="O51">
-        <f>TTEST(H51:M51,B51:G51,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.42470698255588146</v>
       </c>
       <c r="P51" s="1">
-        <f>(N51-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-36.45612940102567</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3437,19 +3650,19 @@
         <v>4.1247233225937142E-3</v>
       </c>
       <c r="N52">
-        <f>AVERAGE(H52:M52)/AVERAGE(B52:G52)</f>
+        <f t="shared" si="3"/>
         <v>0.76642857257828567</v>
       </c>
       <c r="O52">
-        <f>TTEST(H52:M52,B52:G52,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.4361528973393024</v>
       </c>
       <c r="P52" s="1">
-        <f>(N52-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-23.357142742171433</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -3490,19 +3703,19 @@
         <v>95.254752540131562</v>
       </c>
       <c r="N53">
-        <f>AVERAGE(H53:M53)/AVERAGE(B53:G53)</f>
+        <f t="shared" si="3"/>
         <v>0.93625766264422394</v>
       </c>
       <c r="O53">
-        <f>TTEST(H53:M53,B53:G53,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.44008590101421219</v>
       </c>
       <c r="P53" s="1">
-        <f>(N53-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-6.3742337355776062</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -3543,19 +3756,19 @@
         <v>2.2311883358713766E-3</v>
       </c>
       <c r="N54">
-        <f>AVERAGE(H54:M54)/AVERAGE(B54:G54)</f>
+        <f t="shared" si="3"/>
         <v>0.90131107097528385</v>
       </c>
       <c r="O54">
-        <f>TTEST(H54:M54,B54:G54,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.55051055185459252</v>
       </c>
       <c r="P54" s="1">
-        <f>(N54-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-9.8688929024716145</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -3596,19 +3809,19 @@
         <v>7.4399107467232717E-2</v>
       </c>
       <c r="N55">
-        <f>AVERAGE(H55:M55)/AVERAGE(B55:G55)</f>
+        <f t="shared" si="3"/>
         <v>0.89356064861928919</v>
       </c>
       <c r="O55">
-        <f>TTEST(H55:M55,B55:G55,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.56062900308562147</v>
       </c>
       <c r="P55" s="1">
-        <f>(N55-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-10.643935138071081</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -3649,19 +3862,19 @@
         <v>2.4764106542322362E-2</v>
       </c>
       <c r="N56">
-        <f>AVERAGE(H56:M56)/AVERAGE(B56:G56)</f>
+        <f t="shared" si="3"/>
         <v>0.92519757847516881</v>
       </c>
       <c r="O56">
-        <f>TTEST(H56:M56,B56:G56,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.60063917437455105</v>
       </c>
       <c r="P56" s="1">
-        <f>(N56-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-7.4802421524831182</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -3702,19 +3915,19 @@
         <v>2.331514271501252</v>
       </c>
       <c r="N57">
-        <f>AVERAGE(H57:M57)/AVERAGE(B57:G57)</f>
+        <f t="shared" si="3"/>
         <v>1.0880617730262414</v>
       </c>
       <c r="O57">
-        <f>TTEST(H57:M57,B57:G57,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.60629435924609698</v>
       </c>
       <c r="P57" s="1">
-        <f>(N57-1)*100</f>
+        <f t="shared" si="5"/>
         <v>8.8061773026241408</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -3755,19 +3968,19 @@
         <v>4.6481091071382742E-2</v>
       </c>
       <c r="N58">
-        <f>AVERAGE(H58:M58)/AVERAGE(B58:G58)</f>
+        <f t="shared" si="3"/>
         <v>0.89646440965333718</v>
       </c>
       <c r="O58">
-        <f>TTEST(H58:M58,B58:G58,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.60907546846077554</v>
       </c>
       <c r="P58" s="1">
-        <f>(N58-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-10.353559034666283</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -3808,19 +4021,19 @@
         <v>1.9793532864016573E-3</v>
       </c>
       <c r="N59">
-        <f>AVERAGE(H59:M59)/AVERAGE(B59:G59)</f>
+        <f t="shared" si="3"/>
         <v>0.86604720951653569</v>
       </c>
       <c r="O59">
-        <f>TTEST(H59:M59,B59:G59,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.61112384122752184</v>
       </c>
       <c r="P59" s="1">
-        <f>(N59-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-13.395279048346431</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -3861,19 +4074,19 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <f>AVERAGE(H60:M60)/AVERAGE(B60:G60)</f>
+        <f t="shared" si="3"/>
         <v>1.404849061793084</v>
       </c>
       <c r="O60">
-        <f>TTEST(H60:M60,B60:G60,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.61702297199518075</v>
       </c>
       <c r="P60" s="1">
-        <f>(N60-1)*100</f>
+        <f t="shared" si="5"/>
         <v>40.484906179308396</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -3914,19 +4127,19 @@
         <v>0.195773585090638</v>
       </c>
       <c r="N61">
-        <f>AVERAGE(H61:M61)/AVERAGE(B61:G61)</f>
+        <f t="shared" si="3"/>
         <v>0.93553068728809818</v>
       </c>
       <c r="O61">
-        <f>TTEST(H61:M61,B61:G61,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.63375200519835129</v>
       </c>
       <c r="P61" s="1">
-        <f>(N61-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-6.4469312711901816</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -3967,19 +4180,19 @@
         <v>4.9284592968139446E-3</v>
       </c>
       <c r="N62">
-        <f>AVERAGE(H62:M62)/AVERAGE(B62:G62)</f>
+        <f t="shared" si="3"/>
         <v>1.1191610222502038</v>
       </c>
       <c r="O62">
-        <f>TTEST(H62:M62,B62:G62,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.69183839462052588</v>
       </c>
       <c r="P62" s="1">
-        <f>(N62-1)*100</f>
+        <f t="shared" si="5"/>
         <v>11.916102225020374</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -4020,19 +4233,19 @@
         <v>6.4188119422286E-2</v>
       </c>
       <c r="N63">
-        <f>AVERAGE(H63:M63)/AVERAGE(B63:G63)</f>
+        <f t="shared" si="3"/>
         <v>0.95815416055909397</v>
       </c>
       <c r="O63">
-        <f>TTEST(H63:M63,B63:G63,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.73226287598826012</v>
       </c>
       <c r="P63" s="1">
-        <f>(N63-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-4.184583944090603</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -4073,19 +4286,19 @@
         <v>6.4105030245538283E-3</v>
       </c>
       <c r="N64">
-        <f>AVERAGE(H64:M64)/AVERAGE(B64:G64)</f>
+        <f t="shared" si="3"/>
         <v>0.90064250865291662</v>
       </c>
       <c r="O64">
-        <f>TTEST(H64:M64,B64:G64,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.73777129869380498</v>
       </c>
       <c r="P64" s="1">
-        <f>(N64-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-9.9357491347083382</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -4126,19 +4339,19 @@
         <v>3.817357704589585E-3</v>
       </c>
       <c r="N65">
-        <f>AVERAGE(H65:M65)/AVERAGE(B65:G65)</f>
+        <f t="shared" si="3"/>
         <v>0.95270065419034244</v>
       </c>
       <c r="O65">
-        <f>TTEST(H65:M65,B65:G65,2,3)</f>
+        <f t="shared" si="4"/>
         <v>0.74215275331599073</v>
       </c>
       <c r="P65" s="1">
-        <f>(N65-1)*100</f>
+        <f t="shared" si="5"/>
         <v>-4.7299345809657556</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4179,19 +4392,19 @@
         <v>3.5064539262086615E-2</v>
       </c>
       <c r="N66">
-        <f>AVERAGE(H66:M66)/AVERAGE(B66:G66)</f>
+        <f t="shared" ref="N66:N85" si="6">AVERAGE(H66:M66)/AVERAGE(B66:G66)</f>
         <v>1.0706806018525961</v>
       </c>
       <c r="O66">
-        <f>TTEST(H66:M66,B66:G66,2,3)</f>
+        <f t="shared" ref="O66:O85" si="7">TTEST(H66:M66,B66:G66,2,3)</f>
         <v>0.74745789065968582</v>
       </c>
       <c r="P66" s="1">
-        <f>(N66-1)*100</f>
+        <f t="shared" ref="P66:P85" si="8">(N66-1)*100</f>
         <v>7.0680601852596059</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -4232,19 +4445,19 @@
         <v>0.27484646866844037</v>
       </c>
       <c r="N67">
-        <f>AVERAGE(H67:M67)/AVERAGE(B67:G67)</f>
+        <f t="shared" si="6"/>
         <v>1.0631201270940909</v>
       </c>
       <c r="O67">
-        <f>TTEST(H67:M67,B67:G67,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.75665220445047954</v>
       </c>
       <c r="P67" s="1">
-        <f>(N67-1)*100</f>
+        <f t="shared" si="8"/>
         <v>6.3120127094090872</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -4285,19 +4498,19 @@
         <v>1.6349305565004142E-2</v>
       </c>
       <c r="N68">
-        <f>AVERAGE(H68:M68)/AVERAGE(B68:G68)</f>
+        <f t="shared" si="6"/>
         <v>1.0510505641718977</v>
       </c>
       <c r="O68">
-        <f>TTEST(H68:M68,B68:G68,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.76544317913547655</v>
       </c>
       <c r="P68" s="1">
-        <f>(N68-1)*100</f>
+        <f t="shared" si="8"/>
         <v>5.1050564171897683</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -4338,19 +4551,19 @@
         <v>0.10628800667671744</v>
       </c>
       <c r="N69">
-        <f>AVERAGE(H69:M69)/AVERAGE(B69:G69)</f>
+        <f t="shared" si="6"/>
         <v>1.0423603540439159</v>
       </c>
       <c r="O69">
-        <f>TTEST(H69:M69,B69:G69,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.76813206334445217</v>
       </c>
       <c r="P69" s="1">
-        <f>(N69-1)*100</f>
+        <f t="shared" si="8"/>
         <v>4.2360354043915915</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -4391,19 +4604,19 @@
         <v>4.7601442773536701E-2</v>
       </c>
       <c r="N70">
-        <f>AVERAGE(H70:M70)/AVERAGE(B70:G70)</f>
+        <f t="shared" si="6"/>
         <v>0.93127970469698607</v>
       </c>
       <c r="O70">
-        <f>TTEST(H70:M70,B70:G70,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.76943267221258727</v>
       </c>
       <c r="P70" s="1">
-        <f>(N70-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-6.8720295303013934</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -4444,19 +4657,19 @@
         <v>2.4677777832597956E-3</v>
       </c>
       <c r="N71">
-        <f>AVERAGE(H71:M71)/AVERAGE(B71:G71)</f>
+        <f t="shared" si="6"/>
         <v>1.0919924527078142</v>
       </c>
       <c r="O71">
-        <f>TTEST(H71:M71,B71:G71,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.77041026368426935</v>
       </c>
       <c r="P71" s="1">
-        <f>(N71-1)*100</f>
+        <f t="shared" si="8"/>
         <v>9.1992452707814198</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -4497,19 +4710,19 @@
         <v>1.1708951526396965</v>
       </c>
       <c r="N72">
-        <f>AVERAGE(H72:M72)/AVERAGE(B72:G72)</f>
+        <f t="shared" si="6"/>
         <v>0.9476814805398448</v>
       </c>
       <c r="O72">
-        <f>TTEST(H72:M72,B72:G72,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.77787897755414348</v>
       </c>
       <c r="P72" s="1">
-        <f>(N72-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-5.2318519460155199</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -4550,19 +4763,19 @@
         <v>4.2544044089065272E-2</v>
       </c>
       <c r="N73">
-        <f>AVERAGE(H73:M73)/AVERAGE(B73:G73)</f>
+        <f t="shared" si="6"/>
         <v>1.0571752852648748</v>
       </c>
       <c r="O73">
-        <f>TTEST(H73:M73,B73:G73,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.79955980612503019</v>
       </c>
       <c r="P73" s="1">
-        <f>(N73-1)*100</f>
+        <f t="shared" si="8"/>
         <v>5.7175285264874809</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -4603,19 +4816,19 @@
         <v>1.6861624810355684E-2</v>
       </c>
       <c r="N74">
-        <f>AVERAGE(H74:M74)/AVERAGE(B74:G74)</f>
+        <f t="shared" si="6"/>
         <v>0.97736072652151673</v>
       </c>
       <c r="O74">
-        <f>TTEST(H74:M74,B74:G74,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.82514296853771496</v>
       </c>
       <c r="P74" s="1">
-        <f>(N74-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-2.2639273478483268</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -4656,19 +4869,19 @@
         <v>0.22070009308082467</v>
       </c>
       <c r="N75">
-        <f>AVERAGE(H75:M75)/AVERAGE(B75:G75)</f>
+        <f t="shared" si="6"/>
         <v>1.0254328631123801</v>
       </c>
       <c r="O75">
-        <f>TTEST(H75:M75,B75:G75,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.8496515869445187</v>
       </c>
       <c r="P75" s="1">
-        <f>(N75-1)*100</f>
+        <f t="shared" si="8"/>
         <v>2.5432863112380133</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -4709,19 +4922,19 @@
         <v>8.435009818702216E-2</v>
       </c>
       <c r="N76">
-        <f>AVERAGE(H76:M76)/AVERAGE(B76:G76)</f>
+        <f t="shared" si="6"/>
         <v>0.97430645265035332</v>
       </c>
       <c r="O76">
-        <f>TTEST(H76:M76,B76:G76,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.85628811029036733</v>
       </c>
       <c r="P76" s="1">
-        <f>(N76-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-2.5693547349646684</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -4762,19 +4975,19 @@
         <v>1.770589784024799E-3</v>
       </c>
       <c r="N77">
-        <f>AVERAGE(H77:M77)/AVERAGE(B77:G77)</f>
+        <f t="shared" si="6"/>
         <v>1.0692131035489112</v>
       </c>
       <c r="O77">
-        <f>TTEST(H77:M77,B77:G77,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.8713145873241519</v>
       </c>
       <c r="P77" s="1">
-        <f>(N77-1)*100</f>
+        <f t="shared" si="8"/>
         <v>6.9213103548911192</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -4815,19 +5028,19 @@
         <v>1.7326185520358358E-2</v>
       </c>
       <c r="N78">
-        <f>AVERAGE(H78:M78)/AVERAGE(B78:G78)</f>
+        <f t="shared" si="6"/>
         <v>0.98495049955906855</v>
       </c>
       <c r="O78">
-        <f>TTEST(H78:M78,B78:G78,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.90812197192176491</v>
       </c>
       <c r="P78" s="1">
-        <f>(N78-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-1.5049500440931451</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -4868,19 +5081,19 @@
         <v>8.9514494392799388E-4</v>
       </c>
       <c r="N79">
-        <f>AVERAGE(H79:M79)/AVERAGE(B79:G79)</f>
+        <f t="shared" si="6"/>
         <v>1.0148900500966023</v>
       </c>
       <c r="O79">
-        <f>TTEST(H79:M79,B79:G79,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.93978457047453878</v>
       </c>
       <c r="P79" s="1">
-        <f>(N79-1)*100</f>
+        <f t="shared" si="8"/>
         <v>1.489005009660227</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -4921,19 +5134,19 @@
         <v>3.3563952543158092E-3</v>
       </c>
       <c r="N80">
-        <f>AVERAGE(H80:M80)/AVERAGE(B80:G80)</f>
+        <f t="shared" si="6"/>
         <v>0.99029967702849131</v>
       </c>
       <c r="O80">
-        <f>TTEST(H80:M80,B80:G80,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.94978108107659798</v>
       </c>
       <c r="P80" s="1">
-        <f>(N80-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-0.97003229715086903</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -4974,19 +5187,19 @@
         <v>0.20079467012201621</v>
       </c>
       <c r="N81">
-        <f>AVERAGE(H81:M81)/AVERAGE(B81:G81)</f>
+        <f t="shared" si="6"/>
         <v>0.99223233354913742</v>
       </c>
       <c r="O81">
-        <f>TTEST(H81:M81,B81:G81,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.95033032550197483</v>
       </c>
       <c r="P81" s="1">
-        <f>(N81-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-0.77676664508625759</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>80</v>
       </c>
@@ -5027,19 +5240,19 @@
         <v>1.7540470206407848E-2</v>
       </c>
       <c r="N82">
-        <f>AVERAGE(H82:M82)/AVERAGE(B82:G82)</f>
+        <f t="shared" si="6"/>
         <v>1.003450913747981</v>
       </c>
       <c r="O82">
-        <f>TTEST(H82:M82,B82:G82,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.97849935196756932</v>
       </c>
       <c r="P82" s="1">
-        <f>(N82-1)*100</f>
+        <f t="shared" si="8"/>
         <v>0.34509137479810104</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -5080,19 +5293,19 @@
         <v>0.17612275042248132</v>
       </c>
       <c r="N83">
-        <f>AVERAGE(H83:M83)/AVERAGE(B83:G83)</f>
+        <f t="shared" si="6"/>
         <v>0.99661103816401464</v>
       </c>
       <c r="O83">
-        <f>TTEST(H83:M83,B83:G83,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.97927458288189739</v>
       </c>
       <c r="P83" s="1">
-        <f>(N83-1)*100</f>
+        <f t="shared" si="8"/>
         <v>-0.33889618359853602</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>82</v>
       </c>
@@ -5133,19 +5346,19 @@
         <v>9.0597917679461903E-3</v>
       </c>
       <c r="N84">
-        <f>AVERAGE(H84:M84)/AVERAGE(B84:G84)</f>
+        <f t="shared" si="6"/>
         <v>1.0052332285640677</v>
       </c>
       <c r="O84">
-        <f>TTEST(H84:M84,B84:G84,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.98483651932071004</v>
       </c>
       <c r="P84" s="1">
-        <f>(N84-1)*100</f>
+        <f t="shared" si="8"/>
         <v>0.52332285640677156</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -5186,15 +5399,15 @@
         <v>9.0108998991213024E-2</v>
       </c>
       <c r="N85">
-        <f>AVERAGE(H85:M85)/AVERAGE(B85:G85)</f>
+        <f t="shared" si="6"/>
         <v>1.0001305315721762</v>
       </c>
       <c r="O85">
-        <f>TTEST(H85:M85,B85:G85,2,3)</f>
+        <f t="shared" si="7"/>
         <v>0.99948811788669967</v>
       </c>
       <c r="P85" s="1">
-        <f>(N85-1)*100</f>
+        <f t="shared" si="8"/>
         <v>1.3053157217624012E-2</v>
       </c>
     </row>
@@ -5206,4 +5419,280 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A39AC12-F7D6-45A6-8978-152EBCC9B0E9}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>